--- a/docs/2320110211_최강현_개발산출물.xlsx
+++ b/docs/2320110211_최강현_개발산출물.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="345">
   <si>
     <t>사용자</t>
   </si>
@@ -2542,6 +2542,21 @@
       <t>삭제</t>
     </r>
     <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>Web Push (VAPID) 구독 등록 구현 (v1 범위 외)</t>
+  </si>
+  <si>
+    <t>SSE/Web Push 자동 분기 로직 구현 (v1 범위 외)</t>
+  </si>
+  <si>
+    <t>키워드 뉴스 도착 알림 발행</t>
+  </si>
+  <si>
+    <t>피드 소스/키워드 필터링</t>
+  </si>
+  <si>
+    <t>회원 탈퇴</t>
   </si>
 </sst>
 </file>
@@ -8726,7 +8741,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T71"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47" style="1" customWidth="1"/>
@@ -8781,7 +8796,7 @@
         <v>327</v>
       </c>
       <c r="C2" s="28" t="str">
-        <f t="shared" ref="C2:C45" si="0">IF(G2=0,"Not Started",IF(G2&lt;1,"In Progress",IF(G2=1,"Finished")))</f>
+        <f t="shared" ref="C2:C46" si="0">IF(G2=0,"Not Started",IF(G2&lt;1,"In Progress",IF(G2=1,"Finished")))</f>
         <v>Finished</v>
       </c>
       <c r="D2" s="29">
@@ -8791,7 +8806,7 @@
         <v>45751</v>
       </c>
       <c r="F2" s="27">
-        <f t="shared" ref="F2:F45" si="1">NETWORKDAYS(D2,E2)</f>
+        <f t="shared" ref="F2:F46" si="1">NETWORKDAYS(D2,E2)</f>
         <v>24</v>
       </c>
       <c r="G2" s="27">
@@ -9272,7 +9287,7 @@
         <v>327</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D15" s="29">
         <v>45752</v>
@@ -9285,7 +9300,7 @@
         <v>45</v>
       </c>
       <c r="G15" s="27">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -9309,7 +9324,7 @@
         <v>327</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D16" s="29">
         <v>45752</v>
@@ -9322,7 +9337,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="27">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -9416,25 +9431,25 @@
       <c r="A19" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="61" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="28" t="str">
+      <c r="C19" s="53" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="D19" s="30">
+        <v>Finished</v>
+      </c>
+      <c r="D19" s="54">
         <v>45752</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="54">
         <v>45765</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="55">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G19" s="7">
-        <v>0</v>
+      <c r="G19" s="55">
+        <v>1</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -9458,7 +9473,7 @@
         <v>327</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D20" s="29">
         <v>45768</v>
@@ -9471,7 +9486,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="27">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -9491,24 +9506,24 @@
       <c r="A21" s="34" t="s">
         <v>296</v>
       </c>
-      <c r="B21" s="60" t="s">
+      <c r="B21" s="61" t="s">
         <v>330</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>324</v>
-      </c>
-      <c r="D21" s="30">
+      <c r="C21" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D21" s="54">
         <v>45768</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="54">
         <v>45786</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="55">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G21" s="7">
-        <v>0.8</v>
+      <c r="G21" s="55">
+        <v>1</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -9565,25 +9580,25 @@
       <c r="A23" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="61" t="s">
         <v>330</v>
       </c>
-      <c r="C23" s="28" t="str">
+      <c r="C23" s="53" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="D23" s="30">
+        <v>Finished</v>
+      </c>
+      <c r="D23" s="54">
         <v>45768</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="54">
         <v>45786</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="55">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G23" s="7">
-        <v>0</v>
+      <c r="G23" s="55">
+        <v>1</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -9601,27 +9616,27 @@
     </row>
     <row r="24" spans="1:20" ht="16.5" customHeight="1">
       <c r="A24" s="34" t="s">
-        <v>298</v>
-      </c>
-      <c r="B24" s="60" t="s">
+        <v>342</v>
+      </c>
+      <c r="B24" s="61" t="s">
         <v>330</v>
       </c>
-      <c r="C24" s="28" t="str">
+      <c r="C24" s="53" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="D24" s="30">
+        <v>Finished</v>
+      </c>
+      <c r="D24" s="54">
         <v>45768</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="54">
         <v>45786</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="55">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G24" s="7">
-        <v>0</v>
+      <c r="G24" s="55">
+        <v>1</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -9711,27 +9726,26 @@
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
     </row>
-    <row r="27" spans="1:20" ht="15" customHeight="1">
-      <c r="A27" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="B27" s="59" t="s">
-        <v>328</v>
-      </c>
-      <c r="C27" s="28" t="s">
+    <row r="27" spans="1:20" ht="16.5" customHeight="1">
+      <c r="A27" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C27" s="53" t="s">
         <v>323</v>
       </c>
-      <c r="D27" s="29">
-        <v>45789</v>
-      </c>
-      <c r="E27" s="29">
-        <v>45807</v>
-      </c>
-      <c r="F27" s="27">
-        <f t="shared" si="1"/>
+      <c r="D27" s="54">
+        <v>45768</v>
+      </c>
+      <c r="E27" s="54">
+        <v>45786</v>
+      </c>
+      <c r="F27" s="55">
         <v>15</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="55">
         <v>1</v>
       </c>
       <c r="H27" s="2"/>
@@ -9748,27 +9762,27 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
     </row>
-    <row r="28" spans="1:20" ht="16.5" customHeight="1">
-      <c r="A28" s="57" t="s">
-        <v>301</v>
-      </c>
-      <c r="B28" s="61" t="s">
+    <row r="28" spans="1:20" ht="15" customHeight="1">
+      <c r="A28" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="B28" s="59" t="s">
         <v>328</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="29">
         <v>45789</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="29">
         <v>45807</v>
       </c>
-      <c r="F28" s="55">
+      <c r="F28" s="27">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="27">
         <v>1</v>
       </c>
       <c r="H28" s="2"/>
@@ -9786,8 +9800,8 @@
       <c r="T28" s="2"/>
     </row>
     <row r="29" spans="1:20" ht="16.5" customHeight="1">
-      <c r="A29" s="56" t="s">
-        <v>337</v>
+      <c r="A29" s="57" t="s">
+        <v>301</v>
       </c>
       <c r="B29" s="61" t="s">
         <v>328</v>
@@ -9802,7 +9816,7 @@
         <v>45807</v>
       </c>
       <c r="F29" s="55">
-        <f t="shared" ref="F29" si="3">NETWORKDAYS(D29,E29)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="G29" s="55">
@@ -9824,7 +9838,7 @@
     </row>
     <row r="30" spans="1:20" ht="16.5" customHeight="1">
       <c r="A30" s="56" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B30" s="61" t="s">
         <v>328</v>
@@ -9839,7 +9853,7 @@
         <v>45807</v>
       </c>
       <c r="F30" s="55">
-        <f t="shared" ref="F30" si="4">NETWORKDAYS(D30,E30)</f>
+        <f t="shared" ref="F30" si="3">NETWORKDAYS(D30,E30)</f>
         <v>15</v>
       </c>
       <c r="G30" s="55">
@@ -9861,7 +9875,7 @@
     </row>
     <row r="31" spans="1:20" ht="16.5" customHeight="1">
       <c r="A31" s="56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B31" s="61" t="s">
         <v>328</v>
@@ -9876,7 +9890,7 @@
         <v>45807</v>
       </c>
       <c r="F31" s="55">
-        <f t="shared" ref="F31" si="5">NETWORKDAYS(D31,E31)</f>
+        <f t="shared" ref="F31" si="4">NETWORKDAYS(D31,E31)</f>
         <v>15</v>
       </c>
       <c r="G31" s="55">
@@ -9896,9 +9910,9 @@
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
     </row>
-    <row r="32" spans="1:20" ht="15" customHeight="1">
+    <row r="32" spans="1:20" ht="16.5" customHeight="1">
       <c r="A32" s="56" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="B32" s="61" t="s">
         <v>328</v>
@@ -9913,7 +9927,7 @@
         <v>45807</v>
       </c>
       <c r="F32" s="55">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F32" si="5">NETWORKDAYS(D32,E32)</f>
         <v>15</v>
       </c>
       <c r="G32" s="55">
@@ -9935,7 +9949,7 @@
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1">
       <c r="A33" s="56" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B33" s="61" t="s">
         <v>328</v>
@@ -9971,8 +9985,8 @@
       <c r="T33" s="2"/>
     </row>
     <row r="34" spans="1:20" ht="15" customHeight="1">
-      <c r="A34" s="57" t="s">
-        <v>304</v>
+      <c r="A34" s="56" t="s">
+        <v>303</v>
       </c>
       <c r="B34" s="61" t="s">
         <v>328</v>
@@ -9984,19 +9998,32 @@
         <v>45789</v>
       </c>
       <c r="E34" s="54">
-        <v>45793</v>
+        <v>45807</v>
       </c>
       <c r="F34" s="55">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G34" s="55">
         <v>1</v>
       </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
     </row>
     <row r="35" spans="1:20" ht="15" customHeight="1">
       <c r="A35" s="57" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="B35" s="61" t="s">
         <v>328</v>
@@ -10020,7 +10047,7 @@
     </row>
     <row r="36" spans="1:20" ht="15" customHeight="1">
       <c r="A36" s="57" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B36" s="61" t="s">
         <v>328</v>
@@ -10029,10 +10056,10 @@
         <v>323</v>
       </c>
       <c r="D36" s="54">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="E36" s="54">
-        <v>45800</v>
+        <v>45793</v>
       </c>
       <c r="F36" s="55">
         <f t="shared" si="1"/>
@@ -10044,7 +10071,7 @@
     </row>
     <row r="37" spans="1:20" ht="15" customHeight="1">
       <c r="A37" s="57" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B37" s="61" t="s">
         <v>328</v>
@@ -10067,56 +10094,56 @@
       </c>
     </row>
     <row r="38" spans="1:20" ht="15" customHeight="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="B38" s="61" t="s">
+        <v>328</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D38" s="54">
+        <v>45796</v>
+      </c>
+      <c r="E38" s="54">
+        <v>45800</v>
+      </c>
+      <c r="F38" s="55">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G38" s="55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15" customHeight="1">
+      <c r="A39" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="B38" s="59" t="s">
+      <c r="B39" s="59" t="s">
         <v>331</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C39" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D39" s="29">
         <v>45803</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E39" s="29">
         <v>45814</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F39" s="32">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G38" s="32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15" customHeight="1">
-      <c r="A39" s="57" t="s">
-        <v>306</v>
-      </c>
-      <c r="B39" s="61" t="s">
-        <v>327</v>
-      </c>
-      <c r="C39" s="53" t="s">
-        <v>323</v>
-      </c>
-      <c r="D39" s="54">
-        <v>45803</v>
-      </c>
-      <c r="E39" s="54">
-        <v>45807</v>
-      </c>
-      <c r="F39" s="55">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="G39" s="55">
+      <c r="G39" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1">
       <c r="A40" s="57" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B40" s="61" t="s">
         <v>327</v>
@@ -10125,10 +10152,10 @@
         <v>323</v>
       </c>
       <c r="D40" s="54">
-        <v>45810</v>
+        <v>45803</v>
       </c>
       <c r="E40" s="54">
-        <v>45814</v>
+        <v>45807</v>
       </c>
       <c r="F40" s="55">
         <f t="shared" si="1"/>
@@ -10139,8 +10166,8 @@
       </c>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1">
-      <c r="A41" s="58" t="s">
-        <v>308</v>
+      <c r="A41" s="57" t="s">
+        <v>307</v>
       </c>
       <c r="B41" s="61" t="s">
         <v>327</v>
@@ -10163,84 +10190,83 @@
       </c>
     </row>
     <row r="42" spans="1:20" ht="15" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="B42" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D42" s="54">
+        <v>45810</v>
+      </c>
+      <c r="E42" s="54">
+        <v>45814</v>
+      </c>
+      <c r="F42" s="55">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G42" s="55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15" customHeight="1">
+      <c r="A43" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="B42" s="59" t="s">
+      <c r="B43" s="59" t="s">
         <v>327</v>
       </c>
-      <c r="C42" s="28" t="str">
+      <c r="C43" s="28" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="D42" s="29">
+        <v>Finished</v>
+      </c>
+      <c r="D43" s="29">
         <v>45810</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E43" s="29">
         <v>45821</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F43" s="32">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G42" s="32">
-        <f>AVERAGE(G43:G45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1">
-      <c r="A43" s="34" t="s">
+      <c r="G43" s="32">
+        <f>G44</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15" customHeight="1">
+      <c r="A44" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="B43" s="60" t="s">
+      <c r="B44" s="61" t="s">
         <v>327</v>
       </c>
-      <c r="C43" s="28" t="str">
+      <c r="C44" s="53" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="D43" s="30">
+        <v>Finished</v>
+      </c>
+      <c r="D44" s="54">
         <v>45810</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E44" s="54">
         <v>45814</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F44" s="55">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G43" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1">
-      <c r="A44" s="34" t="s">
-        <v>311</v>
-      </c>
-      <c r="B44" s="60" t="s">
-        <v>327</v>
-      </c>
-      <c r="C44" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="D44" s="30">
-        <v>45817</v>
-      </c>
-      <c r="E44" s="30">
-        <v>45821</v>
-      </c>
-      <c r="F44" s="7">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="G44" s="7">
-        <v>0</v>
+      <c r="G44" s="55">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="15" customHeight="1">
       <c r="A45" s="34" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="B45" s="60" t="s">
         <v>327</v>
@@ -10264,64 +10290,52 @@
       </c>
     </row>
     <row r="46" spans="1:20" ht="15" customHeight="1">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="B46" s="60" t="s">
+        <v>327</v>
+      </c>
+      <c r="C46" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="D46" s="30">
+        <v>45817</v>
+      </c>
+      <c r="E46" s="30">
+        <v>45821</v>
+      </c>
+      <c r="F46" s="7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G46" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="15" customHeight="1">
+      <c r="A47" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="59" t="s">
+      <c r="B47" s="59" t="s">
         <v>327</v>
       </c>
-      <c r="C46" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="D46" s="29">
+      <c r="C47" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="D47" s="29">
         <v>45810</v>
       </c>
-      <c r="E46" s="29">
+      <c r="E47" s="29">
         <v>45814</v>
       </c>
-      <c r="F46" s="27">
-        <f>NETWORKDAYS(D34,E34)</f>
-        <v>5</v>
-      </c>
-      <c r="G46" s="27">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
-    </row>
-    <row r="47" spans="1:20" ht="15" customHeight="1">
-      <c r="A47" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="B47" s="60" t="s">
-        <v>327</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="D47" s="30">
-        <v>45810</v>
-      </c>
-      <c r="E47" s="30">
-        <v>45814</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="F47" s="27">
         <f>NETWORKDAYS(D35,E35)</f>
         <v>5</v>
       </c>
-      <c r="G47" s="7">
-        <v>0</v>
+      <c r="G47" s="27">
+        <v>1</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -10339,26 +10353,26 @@
     </row>
     <row r="48" spans="1:20" ht="15" customHeight="1">
       <c r="A48" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="B48" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="B48" s="61" t="s">
         <v>327</v>
       </c>
-      <c r="C48" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="D48" s="30">
+      <c r="C48" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D48" s="54">
         <v>45810</v>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="54">
         <v>45814</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="55">
         <f>NETWORKDAYS(D36,E36)</f>
         <v>5</v>
       </c>
-      <c r="G48" s="7">
-        <v>0</v>
+      <c r="G48" s="55">
+        <v>1</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -10376,26 +10390,26 @@
     </row>
     <row r="49" spans="1:20" ht="15" customHeight="1">
       <c r="A49" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="B49" s="60" t="s">
+        <v>314</v>
+      </c>
+      <c r="B49" s="61" t="s">
         <v>327</v>
       </c>
-      <c r="C49" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="D49" s="30">
+      <c r="C49" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D49" s="54">
         <v>45810</v>
       </c>
-      <c r="E49" s="30">
+      <c r="E49" s="54">
         <v>45814</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="55">
         <f>NETWORKDAYS(D37,E37)</f>
         <v>5</v>
       </c>
-      <c r="G49" s="7">
-        <v>0</v>
+      <c r="G49" s="55">
+        <v>1</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -10412,99 +10426,99 @@
       <c r="T49" s="2"/>
     </row>
     <row r="50" spans="1:20" ht="15" customHeight="1">
-      <c r="A50" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="B50" s="60" t="s">
+      <c r="A50" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="B50" s="61" t="s">
         <v>327</v>
       </c>
-      <c r="C50" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="D50" s="30">
+      <c r="C50" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D50" s="54">
         <v>45810</v>
       </c>
-      <c r="E50" s="30">
+      <c r="E50" s="54">
         <v>45814</v>
       </c>
-      <c r="F50" s="7">
-        <f>NETWORKDAYS(D50,E50)</f>
+      <c r="F50" s="55">
+        <f>NETWORKDAYS(D38,E38)</f>
         <v>5</v>
       </c>
-      <c r="G50" s="7">
-        <v>0</v>
-      </c>
+      <c r="G50" s="55">
+        <v>1</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2"/>
     </row>
     <row r="51" spans="1:20" ht="15" customHeight="1">
       <c r="A51" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="B51" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="B51" s="61" t="s">
         <v>327</v>
       </c>
-      <c r="C51" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="D51" s="30">
+      <c r="C51" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D51" s="54">
         <v>45810</v>
       </c>
-      <c r="E51" s="30">
+      <c r="E51" s="54">
         <v>45814</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="55">
         <f>NETWORKDAYS(D51,E51)</f>
         <v>5</v>
       </c>
-      <c r="G51" s="7">
-        <v>0</v>
+      <c r="G51" s="55">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="15" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="B52" s="59" t="s">
-        <v>329</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="D52" s="29">
-        <v>45817</v>
-      </c>
-      <c r="E52" s="29">
-        <v>45819</v>
-      </c>
-      <c r="F52" s="27" t="e">
-        <f>NETWORKDAYS(#REF!,#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G52" s="27">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="2"/>
-      <c r="T52" s="2"/>
+      <c r="A52" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="B52" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D52" s="54">
+        <v>45810</v>
+      </c>
+      <c r="E52" s="54">
+        <v>45814</v>
+      </c>
+      <c r="F52" s="55">
+        <f>NETWORKDAYS(D52,E52)</f>
+        <v>5</v>
+      </c>
+      <c r="G52" s="55">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:20" ht="15" customHeight="1">
       <c r="A53" s="26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B53" s="59" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D53" s="29">
         <v>45817</v>
@@ -10513,10 +10527,11 @@
         <v>45819</v>
       </c>
       <c r="F53" s="27">
-        <v>5</v>
+        <f>NETWORKDAYS(D53,E53)</f>
+        <v>3</v>
       </c>
       <c r="G53" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -10534,13 +10549,13 @@
     </row>
     <row r="54" spans="1:20" ht="15" customHeight="1">
       <c r="A54" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B54" s="59" t="s">
         <v>327</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D54" s="29">
         <v>45817</v>
@@ -10549,11 +10564,10 @@
         <v>45819</v>
       </c>
       <c r="F54" s="27">
-        <f>NETWORKDAYS(D39,E39)</f>
         <v>5</v>
       </c>
       <c r="G54" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -10570,13 +10584,28 @@
       <c r="T54" s="2"/>
     </row>
     <row r="55" spans="1:20" ht="15" customHeight="1">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
+      <c r="A55" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B55" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="D55" s="29">
+        <v>45817</v>
+      </c>
+      <c r="E55" s="29">
+        <v>45819</v>
+      </c>
+      <c r="F55" s="27">
+        <f>NETWORKDAYS(D40,E40)</f>
+        <v>5</v>
+      </c>
+      <c r="G55" s="27">
+        <v>0.5</v>
+      </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -10591,7 +10620,7 @@
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
     </row>
-    <row r="56" spans="1:20">
+    <row r="56" spans="1:20" ht="15" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -10921,6 +10950,28 @@
       <c r="S70" s="2"/>
       <c r="T70" s="2"/>
     </row>
+    <row r="71" spans="1:20">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
